--- a/site/StructureDefinition-hcen-diagnostico.xlsx
+++ b/site/StructureDefinition-hcen-diagnostico.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>0.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-06T01:23:13-03:00</t>
+    <t>2026-10-28T18:02:56-03:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -768,9 +768,6 @@
     <t>Coding.display</t>
   </si>
   <si>
-    <t>section/entry/observation/code/@displayName</t>
-  </si>
-  <si>
     <t>C*E.2 - but note this is not well followed</t>
   </si>
   <si>
@@ -866,7 +863,7 @@
 </t>
   </si>
   <si>
-    <t>Código que identifica el diagnóstico (SNOMED CT u otra terminología)</t>
+    <t>Código que identifica el diagnóstico (SNOMED CT u otra terminología, p.ej. un tesauro clínico institucional)</t>
   </si>
   <si>
     <t>0..1 to account for primarily narrative only resources.</t>
@@ -921,6 +918,12 @@
     <t>Condition.code.coding</t>
   </si>
   <si>
+    <t>Slicing abierto por system: además del slice snomed, admite otra codificación con su propio system — p.ej. un código de un tesauro clínico (ver sección 4.7.4 Tesauro clínico)</t>
+  </si>
+  <si>
+    <t>El slicing es abierto por system. Además del slice snomed, se puede incluir una codificación adicional de otro vocabulario — p.ej. un código de un tesauro clínico (ver [Tesauro clínico](hcen-terminologia.html#tesauro-clínico), sección 4.7.4). La URI de ese system depende de la institución de origen y su confirmación es externa a esta guía; no se fija ni se valida en este perfil.</t>
+  </si>
+  <si>
     <t xml:space="preserve">value:system}
 </t>
   </si>
@@ -1204,10 +1207,10 @@
     <t>Condition.onset[x].end</t>
   </si>
   <si>
-    <t>Fecha de fin del problema de salud</t>
-  </si>
-  <si>
-    <t>Indica la fecha de fin del problema de salud.</t>
+    <t>End time with inclusive boundary, if not ongoing</t>
+  </si>
+  <si>
+    <t>The end of the period. If the end of the period is missing, it means no end was known or planned at the time the instance was created. The start may be in the past, and the end date in the future, which means that period is expected/planned to end at that time.</t>
   </si>
   <si>
     <t>The high value includes any matching date/time. i.e. 2012-02-03T10:00:00 is in a period that has an end value of 2012-02-03.</t>
@@ -1217,9 +1220,6 @@
   </si>
   <si>
     <t>Period.end</t>
-  </si>
-  <si>
-    <t>section/entry/observation/effectiveTime/high/@value</t>
   </si>
   <si>
     <t>DR.2</t>
@@ -4665,19 +4665,19 @@
         <v>103</v>
       </c>
       <c r="AK23" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL23" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM23" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AN23" t="s" s="2">
         <v>240</v>
       </c>
-      <c r="AL23" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM23" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AN23" t="s" s="2">
+      <c r="AO23" t="s" s="2">
         <v>241</v>
-      </c>
-      <c r="AO23" t="s" s="2">
-        <v>242</v>
       </c>
       <c r="AP23" t="s" s="2">
         <v>20</v>
@@ -4688,10 +4688,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4714,19 +4714,19 @@
         <v>92</v>
       </c>
       <c r="K24" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="L24" t="s" s="2">
         <v>244</v>
       </c>
-      <c r="L24" t="s" s="2">
+      <c r="M24" t="s" s="2">
         <v>245</v>
       </c>
-      <c r="M24" t="s" s="2">
+      <c r="N24" t="s" s="2">
         <v>246</v>
       </c>
-      <c r="N24" t="s" s="2">
+      <c r="O24" t="s" s="2">
         <v>247</v>
-      </c>
-      <c r="O24" t="s" s="2">
-        <v>248</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>20</v>
@@ -4775,7 +4775,7 @@
         <v>20</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
@@ -4799,10 +4799,10 @@
         <v>20</v>
       </c>
       <c r="AN24" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="AO24" t="s" s="2">
         <v>250</v>
-      </c>
-      <c r="AO24" t="s" s="2">
-        <v>251</v>
       </c>
       <c r="AP24" t="s" s="2">
         <v>20</v>
@@ -4813,10 +4813,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4842,16 +4842,16 @@
         <v>189</v>
       </c>
       <c r="L25" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="M25" t="s" s="2">
         <v>253</v>
       </c>
-      <c r="M25" t="s" s="2">
+      <c r="N25" t="s" s="2">
         <v>254</v>
       </c>
-      <c r="N25" t="s" s="2">
+      <c r="O25" t="s" s="2">
         <v>255</v>
-      </c>
-      <c r="O25" t="s" s="2">
-        <v>256</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>20</v>
@@ -4900,7 +4900,7 @@
         <v>20</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
@@ -4924,10 +4924,10 @@
         <v>20</v>
       </c>
       <c r="AN25" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="AO25" t="s" s="2">
         <v>258</v>
-      </c>
-      <c r="AO25" t="s" s="2">
-        <v>259</v>
       </c>
       <c r="AP25" t="s" s="2">
         <v>20</v>
@@ -4938,10 +4938,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4967,13 +4967,13 @@
         <v>157</v>
       </c>
       <c r="L26" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="M26" t="s" s="2">
         <v>261</v>
       </c>
-      <c r="M26" t="s" s="2">
+      <c r="N26" t="s" s="2">
         <v>262</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>263</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -5002,10 +5002,10 @@
         <v>115</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>20</v>
@@ -5023,7 +5023,7 @@
         <v>20</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -5044,31 +5044,31 @@
         <v>20</v>
       </c>
       <c r="AM26" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="AN26" t="s" s="2">
         <v>265</v>
       </c>
-      <c r="AN26" t="s" s="2">
+      <c r="AO26" t="s" s="2">
         <v>266</v>
       </c>
-      <c r="AO26" t="s" s="2">
+      <c r="AP26" t="s" s="2">
         <v>267</v>
       </c>
-      <c r="AP26" t="s" s="2">
+      <c r="AQ26" t="s" s="2">
         <v>268</v>
-      </c>
-      <c r="AQ26" t="s" s="2">
-        <v>269</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
@@ -5090,14 +5090,14 @@
         <v>157</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" t="s" s="2">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>20</v>
@@ -5122,14 +5122,14 @@
         <v>20</v>
       </c>
       <c r="X27" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="Y27" t="s" s="2">
         <v>274</v>
       </c>
-      <c r="Y27" t="s" s="2">
+      <c r="Z27" t="s" s="2">
         <v>275</v>
       </c>
-      <c r="Z27" t="s" s="2">
-        <v>276</v>
-      </c>
       <c r="AA27" t="s" s="2">
         <v>20</v>
       </c>
@@ -5146,7 +5146,7 @@
         <v>20</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -5158,36 +5158,36 @@
         <v>20</v>
       </c>
       <c r="AJ27" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="AK27" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL27" t="s" s="2">
         <v>277</v>
       </c>
-      <c r="AK27" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL27" t="s" s="2">
+      <c r="AM27" t="s" s="2">
         <v>278</v>
       </c>
-      <c r="AM27" t="s" s="2">
+      <c r="AN27" t="s" s="2">
         <v>279</v>
       </c>
-      <c r="AN27" t="s" s="2">
+      <c r="AO27" t="s" s="2">
         <v>280</v>
       </c>
-      <c r="AO27" t="s" s="2">
+      <c r="AP27" t="s" s="2">
         <v>281</v>
       </c>
-      <c r="AP27" t="s" s="2">
+      <c r="AQ27" t="s" s="2">
         <v>282</v>
-      </c>
-      <c r="AQ27" t="s" s="2">
-        <v>283</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5305,10 +5305,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5428,10 +5428,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5457,10 +5457,10 @@
         <v>201</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>202</v>
+        <v>286</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>203</v>
+        <v>287</v>
       </c>
       <c r="N30" t="s" s="2">
         <v>204</v>
@@ -5503,7 +5503,7 @@
         <v>20</v>
       </c>
       <c r="AB30" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AC30" s="2"/>
       <c r="AD30" t="s" s="2">
@@ -5551,13 +5551,13 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C31" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D31" t="s" s="2">
         <v>20</v>
@@ -5582,10 +5582,10 @@
         <v>201</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="N31" t="s" s="2">
         <v>204</v>
@@ -5655,7 +5655,7 @@
         <v>103</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AL31" t="s" s="2">
         <v>20</v>
@@ -5678,10 +5678,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5799,10 +5799,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5922,10 +5922,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5967,7 +5967,7 @@
       </c>
       <c r="Q34" s="2"/>
       <c r="R34" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="S34" t="s" s="2">
         <v>20</v>
@@ -6024,7 +6024,7 @@
         <v>103</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>20</v>
@@ -6047,10 +6047,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6170,10 +6170,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6235,7 +6235,7 @@
       </c>
       <c r="Y36" s="2"/>
       <c r="Z36" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>20</v>
@@ -6268,7 +6268,7 @@
         <v>103</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AL36" t="s" s="2">
         <v>20</v>
@@ -6291,10 +6291,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6320,10 +6320,10 @@
         <v>189</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" t="s" s="2">
@@ -6391,7 +6391,7 @@
         <v>103</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>20</v>
@@ -6400,10 +6400,10 @@
         <v>20</v>
       </c>
       <c r="AN37" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="AO37" t="s" s="2">
         <v>241</v>
-      </c>
-      <c r="AO37" t="s" s="2">
-        <v>242</v>
       </c>
       <c r="AP37" t="s" s="2">
         <v>20</v>
@@ -6414,10 +6414,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6440,19 +6440,19 @@
         <v>92</v>
       </c>
       <c r="K38" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="L38" t="s" s="2">
         <v>244</v>
       </c>
-      <c r="L38" t="s" s="2">
+      <c r="M38" t="s" s="2">
         <v>245</v>
       </c>
-      <c r="M38" t="s" s="2">
+      <c r="N38" t="s" s="2">
         <v>246</v>
       </c>
-      <c r="N38" t="s" s="2">
+      <c r="O38" t="s" s="2">
         <v>247</v>
-      </c>
-      <c r="O38" t="s" s="2">
-        <v>248</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>20</v>
@@ -6501,7 +6501,7 @@
         <v>20</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -6525,10 +6525,10 @@
         <v>20</v>
       </c>
       <c r="AN38" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="AO38" t="s" s="2">
         <v>250</v>
-      </c>
-      <c r="AO38" t="s" s="2">
-        <v>251</v>
       </c>
       <c r="AP38" t="s" s="2">
         <v>20</v>
@@ -6539,10 +6539,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6568,16 +6568,16 @@
         <v>189</v>
       </c>
       <c r="L39" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="M39" t="s" s="2">
         <v>253</v>
       </c>
-      <c r="M39" t="s" s="2">
+      <c r="N39" t="s" s="2">
         <v>254</v>
       </c>
-      <c r="N39" t="s" s="2">
+      <c r="O39" t="s" s="2">
         <v>255</v>
-      </c>
-      <c r="O39" t="s" s="2">
-        <v>256</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>20</v>
@@ -6626,7 +6626,7 @@
         <v>20</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -6650,10 +6650,10 @@
         <v>20</v>
       </c>
       <c r="AN39" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="AO39" t="s" s="2">
         <v>258</v>
-      </c>
-      <c r="AO39" t="s" s="2">
-        <v>259</v>
       </c>
       <c r="AP39" t="s" s="2">
         <v>20</v>
@@ -6664,10 +6664,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6693,13 +6693,13 @@
         <v>157</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -6725,13 +6725,13 @@
         <v>20</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>20</v>
@@ -6749,7 +6749,7 @@
         <v>20</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -6770,31 +6770,31 @@
         <v>20</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AP40" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AQ40" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
@@ -6813,17 +6813,17 @@
         <v>92</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>20</v>
@@ -6872,7 +6872,7 @@
         <v>20</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>91</v>
@@ -6887,22 +6887,22 @@
         <v>103</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AQ41" t="s" s="2">
         <v>20</v>
@@ -6910,10 +6910,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6936,16 +6936,16 @@
         <v>92</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -6995,7 +6995,7 @@
         <v>20</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -7013,19 +7013,19 @@
         <v>20</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AQ42" t="s" s="2">
         <v>20</v>
@@ -7033,10 +7033,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7059,16 +7059,16 @@
         <v>92</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -7106,7 +7106,7 @@
         <v>20</v>
       </c>
       <c r="AB43" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AC43" s="2"/>
       <c r="AD43" t="s" s="2">
@@ -7116,7 +7116,7 @@
         <v>198</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -7131,22 +7131,22 @@
         <v>103</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AQ43" t="s" s="2">
         <v>20</v>
@@ -7154,13 +7154,13 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C44" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="D44" t="s" s="2">
         <v>20</v>
@@ -7182,16 +7182,16 @@
         <v>92</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -7241,7 +7241,7 @@
         <v>20</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -7259,19 +7259,19 @@
         <v>20</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AQ44" t="s" s="2">
         <v>20</v>
@@ -7279,13 +7279,13 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C45" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="D45" t="s" s="2">
         <v>20</v>
@@ -7307,16 +7307,16 @@
         <v>92</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -7366,7 +7366,7 @@
         <v>20</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7384,19 +7384,19 @@
         <v>20</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AQ45" t="s" s="2">
         <v>20</v>
@@ -7404,10 +7404,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7525,10 +7525,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7648,10 +7648,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7674,16 +7674,16 @@
         <v>92</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -7733,7 +7733,7 @@
         <v>20</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -7742,13 +7742,13 @@
         <v>91</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AJ48" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AL48" t="s" s="2">
         <v>20</v>
@@ -7757,10 +7757,10 @@
         <v>20</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AP48" t="s" s="2">
         <v>20</v>
@@ -7771,10 +7771,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7797,23 +7797,23 @@
         <v>92</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>20</v>
       </c>
       <c r="Q49" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="R49" t="s" s="2">
         <v>20</v>
@@ -7858,7 +7858,7 @@
         <v>20</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -7867,13 +7867,13 @@
         <v>91</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AJ49" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>383</v>
+        <v>20</v>
       </c>
       <c r="AL49" t="s" s="2">
         <v>20</v>
@@ -7922,7 +7922,7 @@
         <v>20</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="L50" t="s" s="2">
         <v>387</v>
@@ -8045,7 +8045,7 @@
         <v>92</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="L51" t="s" s="2">
         <v>394</v>
@@ -8931,7 +8931,7 @@
         <v>20</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="Y58" t="s" s="2">
         <v>428</v>
@@ -8982,7 +8982,7 @@
         <v>165</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="AP58" t="s" s="2">
         <v>20</v>
@@ -9173,7 +9173,7 @@
         <v>20</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="Y60" t="s" s="2">
         <v>440</v>
@@ -9786,7 +9786,7 @@
         <v>20</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="Y65" t="s" s="2">
         <v>455</v>
